--- a/public/downloads/TettehCompressively2022.xlsx
+++ b/public/downloads/TettehCompressively2022.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="56">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>O</t>
@@ -662,10 +685,10 @@
         <v>117</v>
       </c>
       <c r="N3" s="5">
-        <v>395.9282381534576</v>
+        <v>395928.2381534576</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03241858987582557</v>
+        <v>32.41858987582557</v>
       </c>
       <c r="P3" s="5">
         <v>12213</v>
@@ -712,10 +735,10 @@
         <v>117</v>
       </c>
       <c r="N4" s="5">
-        <v>698.8384392261505</v>
+        <v>698838.4392261505</v>
       </c>
       <c r="O4" s="4">
-        <v>0.04325833730895392</v>
+        <v>43.25833730895392</v>
       </c>
       <c r="P4" s="5">
         <v>16155</v>
@@ -762,10 +785,10 @@
         <v>117</v>
       </c>
       <c r="N5" s="5">
-        <v>1103.735795736313</v>
+        <v>1103735.795736313</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1406391177034038</v>
+        <v>140.6391177034038</v>
       </c>
       <c r="P5" s="5">
         <v>7848</v>
@@ -812,10 +835,10 @@
         <v>117</v>
       </c>
       <c r="N6" s="5">
-        <v>790.2692923545837</v>
+        <v>790269.2923545837</v>
       </c>
       <c r="O6" s="4">
-        <v>0.07996249037282037</v>
+        <v>79.96249037282037</v>
       </c>
       <c r="P6" s="5">
         <v>9883</v>
@@ -862,10 +885,10 @@
         <v>117</v>
       </c>
       <c r="N7" s="5">
-        <v>933.5304546356201</v>
+        <v>933530.4546356201</v>
       </c>
       <c r="O7" s="4">
-        <v>0.145909730327543</v>
+        <v>145.909730327543</v>
       </c>
       <c r="P7" s="5">
         <v>6398</v>
@@ -912,10 +935,10 @@
         <v>117</v>
       </c>
       <c r="N8" s="5">
-        <v>86.9410514831543</v>
+        <v>86941.0514831543</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01153217289868077</v>
+        <v>11.53217289868077</v>
       </c>
       <c r="P8" s="5">
         <v>7539</v>
@@ -962,10 +985,10 @@
         <v>117</v>
       </c>
       <c r="N9" s="5">
-        <v>527.9535648822784</v>
+        <v>527953.5648822784</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02933727299857071</v>
+        <v>29.33727299857071</v>
       </c>
       <c r="P9" s="5">
         <v>17996</v>
@@ -1012,10 +1035,10 @@
         <v>117</v>
       </c>
       <c r="N10" s="5">
-        <v>629.610209941864</v>
+        <v>629610.209941864</v>
       </c>
       <c r="O10" s="4">
-        <v>0.0837136298287281</v>
+        <v>83.7136298287281</v>
       </c>
       <c r="P10" s="5">
         <v>7521</v>
@@ -1062,10 +1085,10 @@
         <v>117</v>
       </c>
       <c r="N11" s="5">
-        <v>316.071172952652</v>
+        <v>316071.172952652</v>
       </c>
       <c r="O11" s="4">
-        <v>0.0374669479555064</v>
+        <v>37.4669479555064</v>
       </c>
       <c r="P11" s="5">
         <v>8436</v>
@@ -1112,10 +1135,10 @@
         <v>117</v>
       </c>
       <c r="N12" s="5">
-        <v>147.769294500351</v>
+        <v>147769.294500351</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01829733710999888</v>
+        <v>18.29733710999888</v>
       </c>
       <c r="P12" s="5">
         <v>8076</v>
@@ -1162,10 +1185,10 @@
         <v>117</v>
       </c>
       <c r="N13" s="5">
-        <v>595.396641254425</v>
+        <v>595396.641254425</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07397150469057337</v>
+        <v>73.97150469057337</v>
       </c>
       <c r="P13" s="5">
         <v>8049</v>
@@ -1212,10 +1235,10 @@
         <v>117</v>
       </c>
       <c r="N14" s="5">
-        <v>649.672470331192</v>
+        <v>649672.470331192</v>
       </c>
       <c r="O14" s="4">
-        <v>0.211206914932117</v>
+        <v>211.2069149321171</v>
       </c>
       <c r="P14" s="5">
         <v>3076</v>
@@ -1262,10 +1285,10 @@
         <v>117</v>
       </c>
       <c r="N15" s="5">
-        <v>1709.341728687286</v>
+        <v>1709341.728687286</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2169766093789396</v>
+        <v>216.9766093789396</v>
       </c>
       <c r="P15" s="5">
         <v>7878</v>
@@ -1312,10 +1335,10 @@
         <v>117</v>
       </c>
       <c r="N16" s="5">
-        <v>208.7264161109924</v>
+        <v>208726.4161109924</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09712722946067587</v>
+        <v>97.12722946067586</v>
       </c>
       <c r="P16" s="5">
         <v>2149</v>
@@ -1362,10 +1385,10 @@
         <v>117</v>
       </c>
       <c r="N17" s="5">
-        <v>736.6113793849945</v>
+        <v>736611.3793849945</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1030369813099727</v>
+        <v>103.0369813099727</v>
       </c>
       <c r="P17" s="5">
         <v>7149</v>
@@ -1393,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1404,9 +1427,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1440,8 +1469,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1463,75 +1500,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1030459738006576</v>
+        <v>0.1417547209332446</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1030459738006576</v>
+        <v>0.144069703547994</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1100691925193245</v>
+        <v>0.1255433937441668</v>
       </c>
       <c r="E3" s="4">
-        <v>90.10088781275223</v>
+        <v>92.85022483569712</v>
       </c>
       <c r="F3" s="4">
-        <v>92.71186440677977</v>
+        <v>94.54897053805034</v>
       </c>
       <c r="G3" s="5">
         <v>59</v>
       </c>
       <c r="H3" s="5">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.111996237290767</v>
+      </c>
+      <c r="O3" s="5">
+        <v>58</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.106001456774009</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1057690341913447</v>
+      </c>
+      <c r="R3" s="5">
+        <v>58</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1892388192418217</v>
+        <v>0.3889209264455626</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1845762765950566</v>
+        <v>0.3496014463238054</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1538885456489097</v>
+        <v>0.3388726650448932</v>
       </c>
       <c r="E4" s="4">
-        <v>89.40607012035584</v>
+        <v>91.89691261119825</v>
       </c>
       <c r="F4" s="4">
-        <v>91.48138587735869</v>
+        <v>90.70900017208595</v>
       </c>
       <c r="G4" s="5">
         <v>39</v>
       </c>
       <c r="H4" s="5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -1545,25 +1618,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3496014463238054</v>
+      </c>
+      <c r="O4" s="5">
+        <v>36</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2171383940140157</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1926371567166134</v>
+      </c>
+      <c r="R4" s="5">
+        <v>36</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.07035451038032789</v>
+        <v>0.2131419084798267</v>
       </c>
       <c r="C5" s="4">
-        <v>0.07035451038032789</v>
+        <v>0.2131419084798267</v>
       </c>
       <c r="D5" s="4">
-        <v>0.07580333971870772</v>
+        <v>0.2163764568121166</v>
       </c>
       <c r="E5" s="4">
-        <v>92.53061224489795</v>
+        <v>94.09183673469387</v>
       </c>
       <c r="F5" s="4">
-        <v>96.56040268456375</v>
+        <v>96.78187919463087</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
@@ -1586,25 +1677,43 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.2131419084798267</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.01505007154390796</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.01505007154390796</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.08183562748932932</v>
+        <v>0.1270831209054902</v>
       </c>
       <c r="C6" s="4">
-        <v>0.08183562748932932</v>
+        <v>0.1270831209054902</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1363313401363959</v>
+        <v>0.09189966508533429</v>
       </c>
       <c r="E6" s="4">
-        <v>89.42176870748298</v>
+        <v>92.82312925170066</v>
       </c>
       <c r="F6" s="4">
-        <v>92.48695003728561</v>
+        <v>95.27591349739002</v>
       </c>
       <c r="G6" s="5">
         <v>9</v>
@@ -1627,9 +1736,27 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4">
+        <v>-0.07934986776646763</v>
+      </c>
+      <c r="O6" s="5">
+        <v>9</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.0829998610352304</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.0829998610352304</v>
+      </c>
+      <c r="R6" s="5">
+        <v>9</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1640,6 +1767,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1647,7 +1775,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1658,9 +1786,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1694,8 +1828,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1717,107 +1859,161 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1539253258536175</v>
+        <v>0.8893083541338489</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1514575409414989</v>
+        <v>0.8618580939277454</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1375981132521155</v>
+        <v>1.343582806472633</v>
       </c>
       <c r="E3" s="4">
-        <v>92.00795572466292</v>
+        <v>81.70183327568341</v>
       </c>
       <c r="F3" s="4">
-        <v>93.06696242369091</v>
+        <v>78.71269859325795</v>
       </c>
       <c r="G3" s="5">
         <v>59</v>
       </c>
       <c r="H3" s="5">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.8618580939277454</v>
+      </c>
+      <c r="O3" s="5">
+        <v>40</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4557489181594251</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4024170410905205</v>
+      </c>
+      <c r="R3" s="5">
+        <v>40</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5245789125607729</v>
+        <v>0.7372505630221448</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4995726990232843</v>
+        <v>0.7841660926483121</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4543350526583666</v>
+        <v>0.946502594950855</v>
       </c>
       <c r="E4" s="4">
-        <v>91.96493982208271</v>
+        <v>87.59113901971048</v>
       </c>
       <c r="F4" s="4">
-        <v>88.82808466701199</v>
+        <v>85.16893248436935</v>
       </c>
       <c r="G4" s="5">
         <v>39</v>
       </c>
       <c r="H4" s="5">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I4" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.7841660926483121</v>
+      </c>
+      <c r="O4" s="5">
+        <v>32</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2057144029343028</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1764248345659619</v>
+      </c>
+      <c r="R4" s="5">
+        <v>32</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.366914822241094</v>
+        <v>0.2071135850512718</v>
       </c>
       <c r="C5" s="4">
-        <v>0.366914822241094</v>
+        <v>0.2071135850512718</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3491755262816213</v>
+        <v>0.2063948960864281</v>
       </c>
       <c r="E5" s="4">
-        <v>93.85714285714286</v>
+        <v>92.4251700680272</v>
       </c>
       <c r="F5" s="4">
-        <v>95.48322147651007</v>
+        <v>95.77181208053692</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
@@ -1840,34 +2036,52 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>0.01090056739208478</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2092936985296888</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2092936985296888</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.3016444982719469</v>
+        <v>1.79906782756593</v>
       </c>
       <c r="C6" s="4">
-        <v>0.3003956737347302</v>
+        <v>1.814132308164891</v>
       </c>
       <c r="D6" s="4">
-        <v>0.1724550069999743</v>
+        <v>2.405987857947875</v>
       </c>
       <c r="E6" s="4">
-        <v>89.6485260770975</v>
+        <v>79.7052154195012</v>
       </c>
       <c r="F6" s="4">
-        <v>88.73104648272459</v>
+        <v>74.78995774297807</v>
       </c>
       <c r="G6" s="5">
         <v>9</v>
       </c>
       <c r="H6" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I6" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6" s="5">
         <v>0</v>
@@ -1881,9 +2095,27 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4">
+        <v>1.814132308164891</v>
+      </c>
+      <c r="O6" s="5">
+        <v>6</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.04237221863425956</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.0245014891406233</v>
+      </c>
+      <c r="R6" s="5">
+        <v>6</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1894,6 +2126,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1901,7 +2134,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1912,9 +2145,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1948,8 +2187,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1971,25 +2218,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1084320970101484</v>
+        <v>0.1030459738006576</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1084320970101484</v>
+        <v>0.1030459738006576</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1427036424517525</v>
+        <v>0.1100691925193245</v>
       </c>
       <c r="E3" s="4">
-        <v>87.51297129021103</v>
+        <v>90.10088781275223</v>
       </c>
       <c r="F3" s="4">
-        <v>91.99010351495845</v>
+        <v>92.71186440677977</v>
       </c>
       <c r="G3" s="5">
         <v>59</v>
@@ -2012,25 +2277,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.01967553392841112</v>
+      </c>
+      <c r="O3" s="5">
+        <v>59</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09889051020675876</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09889051020675876</v>
+      </c>
+      <c r="R3" s="5">
+        <v>59</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2126983056893881</v>
+        <v>0.1892388192418217</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2054721066372878</v>
+        <v>0.1845762765950566</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2160343440343338</v>
+        <v>0.1538885456489097</v>
       </c>
       <c r="E4" s="4">
-        <v>85.51543694400839</v>
+        <v>89.40607012035584</v>
       </c>
       <c r="F4" s="4">
-        <v>90.19761372110325</v>
+        <v>91.48138587735869</v>
       </c>
       <c r="G4" s="5">
         <v>39</v>
@@ -2053,25 +2336,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1808580781782845</v>
+      </c>
+      <c r="O4" s="5">
+        <v>38</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.08273850817526113</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08003274887354143</v>
+      </c>
+      <c r="R4" s="5">
+        <v>38</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2040090338194631</v>
+        <v>0.07035451038032789</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2040090338194631</v>
+        <v>0.07035451038032789</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2543704287016652</v>
+        <v>0.07580333971870772</v>
       </c>
       <c r="E5" s="4">
-        <v>81.55102040816327</v>
+        <v>92.53061224489795</v>
       </c>
       <c r="F5" s="4">
-        <v>91.59843400447427</v>
+        <v>96.56040268456375</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
@@ -2094,25 +2395,43 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.07035451038032789</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.03239601270482638</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.03239601270482638</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.05403560474025287</v>
+        <v>0.08183562748932932</v>
       </c>
       <c r="C6" s="4">
-        <v>0.05403560474025287</v>
+        <v>0.08183562748932932</v>
       </c>
       <c r="D6" s="4">
-        <v>0.01937815893961985</v>
+        <v>0.1363313401363959</v>
       </c>
       <c r="E6" s="4">
-        <v>89.93197278911565</v>
+        <v>89.42176870748298</v>
       </c>
       <c r="F6" s="4">
-        <v>92.49937857320407</v>
+        <v>92.48695003728561</v>
       </c>
       <c r="G6" s="5">
         <v>9</v>
@@ -2135,9 +2454,27 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4">
+        <v>0.08117917708303996</v>
+      </c>
+      <c r="O6" s="5">
+        <v>9</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.03087325982139736</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.03087325982139736</v>
+      </c>
+      <c r="R6" s="5">
+        <v>9</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2148,6 +2485,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2155,7 +2493,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2166,9 +2504,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2202,8 +2546,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2225,75 +2577,111 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1047806123122609</v>
+        <v>0.1539253258536175</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1007431792731989</v>
+        <v>0.1514575409414989</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1198886541926</v>
+        <v>0.1375981132521155</v>
       </c>
       <c r="E3" s="4">
-        <v>92.41611898996889</v>
+        <v>92.00795572466292</v>
       </c>
       <c r="F3" s="4">
-        <v>93.15436241610615</v>
+        <v>93.06696242369091</v>
       </c>
       <c r="G3" s="5">
         <v>59</v>
       </c>
       <c r="H3" s="5">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I3" s="5">
         <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.08234694753577505</v>
+      </c>
+      <c r="O3" s="5">
+        <v>57</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1290145949809649</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1256727493364725</v>
+      </c>
+      <c r="R3" s="5">
+        <v>57</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4252729771657033</v>
+        <v>0.5245789125607729</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3986491367604063</v>
+        <v>0.4995726990232843</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3514870730394138</v>
+        <v>0.4543350526583666</v>
       </c>
       <c r="E4" s="4">
-        <v>91.342229199372</v>
+        <v>91.96493982208271</v>
       </c>
       <c r="F4" s="4">
-        <v>90.01806917914065</v>
+        <v>88.82808466701199</v>
       </c>
       <c r="G4" s="5">
         <v>39</v>
       </c>
       <c r="H4" s="5">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2307,25 +2695,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.4995726990232843</v>
+      </c>
+      <c r="O4" s="5">
+        <v>35</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1506435228252336</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1399958589206301</v>
+      </c>
+      <c r="R4" s="5">
+        <v>35</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.414897991796758</v>
+        <v>0.366914822241094</v>
       </c>
       <c r="C5" s="4">
-        <v>0.414897991796758</v>
+        <v>0.366914822241094</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4122719541991017</v>
+        <v>0.3491755262816213</v>
       </c>
       <c r="E5" s="4">
-        <v>94.68367346938776</v>
+        <v>93.85714285714286</v>
       </c>
       <c r="F5" s="4">
-        <v>97.03355704697987</v>
+        <v>95.48322147651007</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
@@ -2348,34 +2754,52 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.366914822241094</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1277418796820325</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1277418796820325</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.1411432300970338</v>
+        <v>0.3016444982719469</v>
       </c>
       <c r="C6" s="4">
-        <v>0.1411432300970338</v>
+        <v>0.3003956737347302</v>
       </c>
       <c r="D6" s="4">
-        <v>0.07177079460197433</v>
+        <v>0.1724550069999743</v>
       </c>
       <c r="E6" s="4">
-        <v>91.16780045351473</v>
+        <v>89.6485260770975</v>
       </c>
       <c r="F6" s="4">
-        <v>93.1916480238628</v>
+        <v>88.73104648272459</v>
       </c>
       <c r="G6" s="5">
         <v>9</v>
       </c>
       <c r="H6" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="5">
         <v>0</v>
@@ -2389,9 +2813,27 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4">
+        <v>-0.3003956737347302</v>
+      </c>
+      <c r="O6" s="5">
+        <v>8</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.0234966064252353</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.02502875462402088</v>
+      </c>
+      <c r="R6" s="5">
+        <v>8</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2402,6 +2844,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2409,7 +2852,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2420,9 +2863,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2456,8 +2905,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2479,25 +2936,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.03535797340907768</v>
+        <v>0.1084320970101484</v>
       </c>
       <c r="C3" s="4">
-        <v>0.03535797340907768</v>
+        <v>0.1084320970101484</v>
       </c>
       <c r="D3" s="4">
-        <v>0.03307137489887436</v>
+        <v>0.1427036424517525</v>
       </c>
       <c r="E3" s="4">
-        <v>99.77458780122218</v>
+        <v>87.51297129021103</v>
       </c>
       <c r="F3" s="4">
-        <v>99.49038789671265</v>
+        <v>91.99010351495845</v>
       </c>
       <c r="G3" s="5">
         <v>59</v>
@@ -2520,34 +2995,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.003993283415827224</v>
+      </c>
+      <c r="O3" s="5">
+        <v>59</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1080936831613495</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1080936831613495</v>
+      </c>
+      <c r="R3" s="5">
+        <v>59</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.05236859192519479</v>
+        <v>0.2126983056893881</v>
       </c>
       <c r="C4" s="4">
-        <v>0.05236859192519479</v>
+        <v>0.2054721066372878</v>
       </c>
       <c r="D4" s="4">
-        <v>0.05088384057194308</v>
+        <v>0.2160343440343338</v>
       </c>
       <c r="E4" s="4">
-        <v>99.72004186289902</v>
+        <v>85.51543694400839</v>
       </c>
       <c r="F4" s="4">
-        <v>99.57035507371079</v>
+        <v>90.19761372110325</v>
       </c>
       <c r="G4" s="5">
         <v>39</v>
       </c>
       <c r="H4" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -2561,25 +3054,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2054721066372878</v>
+      </c>
+      <c r="O4" s="5">
+        <v>38</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.09723620614520948</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.09237869149029621</v>
+      </c>
+      <c r="R4" s="5">
+        <v>38</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.004869952511393194</v>
+        <v>0.2040090338194631</v>
       </c>
       <c r="C5" s="4">
-        <v>0.004869952511393194</v>
+        <v>0.2040090338194631</v>
       </c>
       <c r="D5" s="4">
-        <v>0.00495068849285758</v>
+        <v>0.2543704287016652</v>
       </c>
       <c r="E5" s="4">
-        <v>100</v>
+        <v>81.55102040816327</v>
       </c>
       <c r="F5" s="4">
-        <v>100</v>
+        <v>91.59843400447427</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
@@ -2602,25 +3113,43 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.2040090338194631</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.04593275950380985</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.04593275950380985</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.01010905220984171</v>
+        <v>0.05403560474025287</v>
       </c>
       <c r="C6" s="4">
-        <v>0.01010905220984171</v>
+        <v>0.05403560474025287</v>
       </c>
       <c r="D6" s="4">
-        <v>0.009928400388692657</v>
+        <v>0.01937815893961985</v>
       </c>
       <c r="E6" s="4">
-        <v>100</v>
+        <v>89.93197278911565</v>
       </c>
       <c r="F6" s="4">
-        <v>100</v>
+        <v>92.49937857320407</v>
       </c>
       <c r="G6" s="5">
         <v>9</v>
@@ -2643,9 +3172,27 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4">
+        <v>-0.05151922255410568</v>
+      </c>
+      <c r="O6" s="5">
+        <v>9</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.02541381443241638</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.02541381443241638</v>
+      </c>
+      <c r="R6" s="5">
+        <v>9</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2656,6 +3203,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2663,7 +3211,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2674,9 +3222,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2710,8 +3264,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2733,34 +3295,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4904073673521351</v>
+        <v>0.1047806123122609</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4904073673521351</v>
+        <v>0.1007431792731989</v>
       </c>
       <c r="D3" s="4">
-        <v>0.490704141909215</v>
+        <v>0.1198886541926</v>
       </c>
       <c r="E3" s="4">
-        <v>90.15911449325493</v>
+        <v>92.41611898996889</v>
       </c>
       <c r="F3" s="4">
-        <v>93.58093504720749</v>
+        <v>93.15436241610615</v>
       </c>
       <c r="G3" s="5">
         <v>59</v>
       </c>
       <c r="H3" s="5">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
         <v>0</v>
@@ -2774,66 +3354,102 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.03111875376773236</v>
+      </c>
+      <c r="O3" s="5">
+        <v>58</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1067715328423905</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.10330495625674</v>
+      </c>
+      <c r="R3" s="5">
+        <v>58</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6524614199277848</v>
+        <v>0.4252729771657033</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6461627511148308</v>
+        <v>0.3986491367604063</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6510715962648558</v>
+        <v>0.3514870730394138</v>
       </c>
       <c r="E4" s="4">
-        <v>89.53253096110238</v>
+        <v>91.342229199372</v>
       </c>
       <c r="F4" s="4">
-        <v>93.15149429243338</v>
+        <v>90.01806917914065</v>
       </c>
       <c r="G4" s="5">
         <v>39</v>
       </c>
       <c r="H4" s="5">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3986491367604063</v>
+      </c>
+      <c r="O4" s="5">
+        <v>37</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1634100531504175</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1441800620826946</v>
+      </c>
+      <c r="R4" s="5">
+        <v>37</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2674173549616597</v>
+        <v>0.414897991796758</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2674173549616597</v>
+        <v>0.414897991796758</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2771892324888967</v>
+        <v>0.4122719541991017</v>
       </c>
       <c r="E5" s="4">
-        <v>90.15306122448979</v>
+        <v>94.68367346938776</v>
       </c>
       <c r="F5" s="4">
-        <v>95.11073825503355</v>
+        <v>97.03355704697987</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
@@ -2856,25 +3472,43 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.414897991796758</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.023024111528905</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.023024111528905</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.8575786194833239</v>
+        <v>0.1411432300970338</v>
       </c>
       <c r="C6" s="4">
-        <v>0.8575786194833239</v>
+        <v>0.1411432300970338</v>
       </c>
       <c r="D6" s="4">
-        <v>0.8584489433267469</v>
+        <v>0.07177079460197433</v>
       </c>
       <c r="E6" s="4">
-        <v>90.62358276643991</v>
+        <v>91.16780045351473</v>
       </c>
       <c r="F6" s="4">
-        <v>93.85160328113348</v>
+        <v>93.1916480238628</v>
       </c>
       <c r="G6" s="5">
         <v>9</v>
@@ -2897,9 +3531,27 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4">
+        <v>-0.1411432300970338</v>
+      </c>
+      <c r="O6" s="5">
+        <v>9</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.06029332227430367</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.06029332227430367</v>
+      </c>
+      <c r="R6" s="5">
+        <v>9</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2910,6 +3562,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2917,7 +3570,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2928,9 +3581,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2964,8 +3623,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2987,25 +3654,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.04426889926683375</v>
+        <v>0.03535797340907768</v>
       </c>
       <c r="C3" s="4">
-        <v>0.04426889926683375</v>
+        <v>0.03535797340907768</v>
       </c>
       <c r="D3" s="4">
-        <v>0.04583419283596567</v>
+        <v>0.03307137489887436</v>
       </c>
       <c r="E3" s="4">
-        <v>99.44482877896921</v>
+        <v>99.77458780122218</v>
       </c>
       <c r="F3" s="4">
-        <v>99.30440222955295</v>
+        <v>99.49038789671265</v>
       </c>
       <c r="G3" s="5">
         <v>59</v>
@@ -3028,34 +3713,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.03362059085391133</v>
+      </c>
+      <c r="O3" s="5">
+        <v>59</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.02146370857655188</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.02146370857655188</v>
+      </c>
+      <c r="R3" s="5">
+        <v>59</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.06058941980197046</v>
+        <v>0.05236859192519479</v>
       </c>
       <c r="C4" s="4">
-        <v>0.05138730813491583</v>
+        <v>0.05236859192519479</v>
       </c>
       <c r="D4" s="4">
-        <v>0.05028769128400858</v>
+        <v>0.05088384057194308</v>
       </c>
       <c r="E4" s="4">
-        <v>99.09471480900066</v>
+        <v>99.72004186289902</v>
       </c>
       <c r="F4" s="4">
-        <v>98.22405782137334</v>
+        <v>99.57035507371079</v>
       </c>
       <c r="G4" s="5">
         <v>39</v>
       </c>
       <c r="H4" s="5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -3069,19 +3772,37 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.05027938924997699</v>
+      </c>
+      <c r="O4" s="5">
+        <v>39</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.04365186941258798</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04365186941258798</v>
+      </c>
+      <c r="R4" s="5">
+        <v>39</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.007186279929544526</v>
+        <v>0.004869952511393194</v>
       </c>
       <c r="C5" s="4">
-        <v>0.007186279929544526</v>
+        <v>0.004869952511393194</v>
       </c>
       <c r="D5" s="4">
-        <v>0.007234155987276836</v>
+        <v>0.00495068849285758</v>
       </c>
       <c r="E5" s="4">
         <v>100</v>
@@ -3110,25 +3831,43 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.001377341231133755</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.005145420757619945</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.005145420757619945</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.05513476746295806</v>
+        <v>0.01010905220984171</v>
       </c>
       <c r="C6" s="4">
-        <v>0.05513476746295806</v>
+        <v>0.01010905220984171</v>
       </c>
       <c r="D6" s="4">
-        <v>0.05981960810239034</v>
+        <v>0.009928400388692657</v>
       </c>
       <c r="E6" s="4">
-        <v>99.98866213151928</v>
+        <v>100</v>
       </c>
       <c r="F6" s="4">
-        <v>99.68307233407904</v>
+        <v>100</v>
       </c>
       <c r="G6" s="5">
         <v>9</v>
@@ -3151,9 +3890,27 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4">
+        <v>-0.000919890896993378</v>
+      </c>
+      <c r="O6" s="5">
+        <v>9</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.01005527003738376</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.01005527003738376</v>
+      </c>
+      <c r="R6" s="5">
+        <v>9</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3164,6 +3921,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3171,7 +3929,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3182,9 +3940,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3218,8 +3982,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3241,25 +4013,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2822649109903326</v>
+        <v>0.4904073673521351</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2822649109903326</v>
+        <v>0.4904073673521351</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2781038723491289</v>
+        <v>0.490704141909215</v>
       </c>
       <c r="E3" s="4">
-        <v>86.88919635650872</v>
+        <v>90.15911449325493</v>
       </c>
       <c r="F3" s="4">
-        <v>92.52132863155499</v>
+        <v>93.58093504720749</v>
       </c>
       <c r="G3" s="5">
         <v>59</v>
@@ -3282,66 +4072,102 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4904073673521351</v>
+      </c>
+      <c r="O3" s="5">
+        <v>59</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1999441870640629</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1999441870640629</v>
+      </c>
+      <c r="R3" s="5">
+        <v>59</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.417969078250437</v>
+        <v>0.6524614199277848</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3992643801400483</v>
+        <v>0.6461627511148308</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3874413734491221</v>
+        <v>0.6510715962648558</v>
       </c>
       <c r="E4" s="4">
-        <v>84.58922030350601</v>
+        <v>89.53253096110238</v>
       </c>
       <c r="F4" s="4">
-        <v>89.35123042505346</v>
+        <v>93.15149429243338</v>
       </c>
       <c r="G4" s="5">
         <v>39</v>
       </c>
       <c r="H4" s="5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.6461627511148308</v>
+      </c>
+      <c r="O4" s="5">
+        <v>38</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.07144052944188135</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06685612011916232</v>
+      </c>
+      <c r="R4" s="5">
+        <v>38</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1652260498011373</v>
+        <v>0.2674173549616597</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1652260498011373</v>
+        <v>0.2674173549616597</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1783277706110738</v>
+        <v>0.2771892324888967</v>
       </c>
       <c r="E5" s="4">
-        <v>84.98979591836735</v>
+        <v>90.15306122448979</v>
       </c>
       <c r="F5" s="4">
-        <v>92.91275167785236</v>
+        <v>95.11073825503355</v>
       </c>
       <c r="G5" s="5">
         <v>10</v>
@@ -3364,25 +4190,43 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.2674173549616597</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.03161599085756961</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.03161599085756961</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.4597823727427645</v>
+        <v>0.8575786194833239</v>
       </c>
       <c r="C6" s="4">
-        <v>0.4597823727427645</v>
+        <v>0.8575786194833239</v>
       </c>
       <c r="D6" s="4">
-        <v>0.4572486455207488</v>
+        <v>0.8584489433267469</v>
       </c>
       <c r="E6" s="4">
-        <v>87.77777777777777</v>
+        <v>90.62358276643991</v>
       </c>
       <c r="F6" s="4">
-        <v>93.24384787472034</v>
+        <v>93.85160328113348</v>
       </c>
       <c r="G6" s="5">
         <v>9</v>
@@ -3405,9 +4249,27 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4">
+        <v>-0.8575786194833239</v>
+      </c>
+      <c r="O6" s="5">
+        <v>9</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.02645954905236442</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.02645954905236442</v>
+      </c>
+      <c r="R6" s="5">
+        <v>9</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3418,12 +4280,1588 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.04426889926683375</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.04426889926683375</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.04583419283596567</v>
+      </c>
+      <c r="E3" s="4">
+        <v>99.44482877896921</v>
+      </c>
+      <c r="F3" s="4">
+        <v>99.30440222955295</v>
+      </c>
+      <c r="G3" s="5">
+        <v>59</v>
+      </c>
+      <c r="H3" s="5">
+        <v>59</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.01489153709106969</v>
+      </c>
+      <c r="O3" s="5">
+        <v>59</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.04317676144002032</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04317676144002032</v>
+      </c>
+      <c r="R3" s="5">
+        <v>59</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.06058941980197046</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.05138730813491583</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.05028769128400858</v>
+      </c>
+      <c r="E4" s="4">
+        <v>99.09471480900066</v>
+      </c>
+      <c r="F4" s="4">
+        <v>98.22405782137334</v>
+      </c>
+      <c r="G4" s="5">
+        <v>39</v>
+      </c>
+      <c r="H4" s="5">
+        <v>38</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.03878930096734067</v>
+      </c>
+      <c r="O4" s="5">
+        <v>38</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.05739908018576124</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04913378329110481</v>
+      </c>
+      <c r="R4" s="5">
+        <v>38</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.007186279929544526</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.007186279929544526</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.007234155987276836</v>
+      </c>
+      <c r="E5" s="4">
+        <v>100</v>
+      </c>
+      <c r="F5" s="4">
+        <v>100</v>
+      </c>
+      <c r="G5" s="5">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5">
+        <v>10</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.007111130734708126</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.006032198138624381</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.006032198138624381</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.05513476746295806</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.05513476746295806</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.05981960810239034</v>
+      </c>
+      <c r="E6" s="4">
+        <v>99.98866213151928</v>
+      </c>
+      <c r="F6" s="4">
+        <v>99.68307233407904</v>
+      </c>
+      <c r="G6" s="5">
+        <v>9</v>
+      </c>
+      <c r="H6" s="5">
+        <v>9</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>0.05513476746295806</v>
+      </c>
+      <c r="O6" s="5">
+        <v>9</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.01909843005033679</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.01909843005033679</v>
+      </c>
+      <c r="R6" s="5">
+        <v>9</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2822649109903326</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2822649109903326</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2781038723491289</v>
+      </c>
+      <c r="E3" s="4">
+        <v>86.88919635650872</v>
+      </c>
+      <c r="F3" s="4">
+        <v>92.52132863155499</v>
+      </c>
+      <c r="G3" s="5">
+        <v>59</v>
+      </c>
+      <c r="H3" s="5">
+        <v>59</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2822649109903326</v>
+      </c>
+      <c r="O3" s="5">
+        <v>59</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1193950713129163</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1193950713129163</v>
+      </c>
+      <c r="R3" s="5">
+        <v>59</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.417969078250437</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3992643801400483</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3874413734491221</v>
+      </c>
+      <c r="E4" s="4">
+        <v>84.58922030350601</v>
+      </c>
+      <c r="F4" s="4">
+        <v>89.35123042505346</v>
+      </c>
+      <c r="G4" s="5">
+        <v>39</v>
+      </c>
+      <c r="H4" s="5">
+        <v>37</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.3992643801400483</v>
+      </c>
+      <c r="O4" s="5">
+        <v>37</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.0778460470660126</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06233817862890089</v>
+      </c>
+      <c r="R4" s="5">
+        <v>37</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.1652260498011373</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.1652260498011373</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.1783277706110738</v>
+      </c>
+      <c r="E5" s="4">
+        <v>84.98979591836735</v>
+      </c>
+      <c r="F5" s="4">
+        <v>92.91275167785236</v>
+      </c>
+      <c r="G5" s="5">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5">
+        <v>10</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.1652260498011373</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.006337371049706919</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.006337371049706919</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.4597823727427645</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.4597823727427645</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.4572486455207488</v>
+      </c>
+      <c r="E6" s="4">
+        <v>87.77777777777777</v>
+      </c>
+      <c r="F6" s="4">
+        <v>93.24384787472034</v>
+      </c>
+      <c r="G6" s="5">
+        <v>9</v>
+      </c>
+      <c r="H6" s="5">
+        <v>9</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>-0.4597823727427645</v>
+      </c>
+      <c r="O6" s="5">
+        <v>9</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.02877508076873371</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.02877508076873371</v>
+      </c>
+      <c r="R6" s="5">
+        <v>9</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>91.45299145299145</v>
+      </c>
+      <c r="C3" s="3">
+        <v>3.418803418803419</v>
+      </c>
+      <c r="D3" s="3">
+        <v>5.128205128205128</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.8547008547008548</v>
+      </c>
+      <c r="F3" s="3">
+        <v>4.273504273504273</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.2319399406966959</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.185936809921913</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.1998038338228532</v>
+      </c>
+      <c r="K3" s="4">
+        <v>91.53235653235566</v>
+      </c>
+      <c r="L3" s="4">
+        <v>91.48243752270572</v>
+      </c>
+      <c r="M3" s="5">
+        <v>117</v>
+      </c>
+      <c r="N3" s="5">
+        <v>395928.2381534576</v>
+      </c>
+      <c r="O3" s="4">
+        <v>32.41858987582557</v>
+      </c>
+      <c r="P3" s="5">
+        <v>12213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>88.88888888888889</v>
+      </c>
+      <c r="C4" s="3">
+        <v>6.837606837606838</v>
+      </c>
+      <c r="D4" s="3">
+        <v>4.273504273504273</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0.8547008547008548</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2.564102564102564</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.8547008547008548</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.3742135135582791</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.3150522277158848</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.3563238988960844</v>
+      </c>
+      <c r="K4" s="4">
+        <v>85.48898191755309</v>
+      </c>
+      <c r="L4" s="4">
+        <v>86.84955735291362</v>
+      </c>
+      <c r="M4" s="5">
+        <v>117</v>
+      </c>
+      <c r="N4" s="5">
+        <v>698838.4392261505</v>
+      </c>
+      <c r="O4" s="4">
+        <v>43.25833730895392</v>
+      </c>
+      <c r="P4" s="5">
+        <v>16155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>99.14529914529915</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.8547008547008548</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.09135188429946133</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.08922471928979626</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.08757835118428076</v>
+      </c>
+      <c r="K5" s="4">
+        <v>89.73196116053261</v>
+      </c>
+      <c r="L5" s="4">
+        <v>93.18562496415097</v>
+      </c>
+      <c r="M5" s="5">
+        <v>117</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1103735.795736313</v>
+      </c>
+      <c r="O5" s="4">
+        <v>140.6391177034038</v>
+      </c>
+      <c r="P5" s="5">
+        <v>7848</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>86.32478632478633</v>
+      </c>
+      <c r="C6" s="3">
+        <v>11.11111111111111</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2.564102564102564</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2.564102564102564</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.2794379231808112</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.2685973565324189</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.2819520998578581</v>
+      </c>
+      <c r="K6" s="4">
+        <v>89.78545264259523</v>
+      </c>
+      <c r="L6" s="4">
+        <v>90.08221954530637</v>
+      </c>
+      <c r="M6" s="5">
+        <v>117</v>
+      </c>
+      <c r="N6" s="5">
+        <v>790269.2923545837</v>
+      </c>
+      <c r="O6" s="4">
+        <v>79.96249037282037</v>
+      </c>
+      <c r="P6" s="5">
+        <v>9883</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>98.29059829059828</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1.70940170940171</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.05401418845012599</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.05118481853728363</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.04960434354934739</v>
+      </c>
+      <c r="K7" s="4">
+        <v>93.92406535263684</v>
+      </c>
+      <c r="L7" s="4">
+        <v>95.1597544886157</v>
+      </c>
+      <c r="M7" s="5">
+        <v>117</v>
+      </c>
+      <c r="N7" s="5">
+        <v>933530.4546356201</v>
+      </c>
+      <c r="O7" s="4">
+        <v>145.909730327543</v>
+      </c>
+      <c r="P7" s="5">
+        <v>6398</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>96.58119658119658</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2.564102564102564</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.8547008547008548</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.8547008547008548</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.133504126333071</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1236021335367454</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.1338788825836971</v>
+      </c>
+      <c r="K8" s="4">
+        <v>92.63649049363318</v>
+      </c>
+      <c r="L8" s="4">
+        <v>93.51574599897015</v>
+      </c>
+      <c r="M8" s="5">
+        <v>117</v>
+      </c>
+      <c r="N8" s="5">
+        <v>86941.0514831543</v>
+      </c>
+      <c r="O8" s="4">
+        <v>11.53217289868077</v>
+      </c>
+      <c r="P8" s="5">
+        <v>7539</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>75.21367521367522</v>
+      </c>
+      <c r="C9" s="3">
+        <v>17.09401709401709</v>
+      </c>
+      <c r="D9" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.3195413234089668</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.2725252530667299</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.4484396193210226</v>
+      </c>
+      <c r="K9" s="4">
+        <v>84.42787371358753</v>
+      </c>
+      <c r="L9" s="4">
+        <v>82.02107114858809</v>
+      </c>
+      <c r="M9" s="5">
+        <v>117</v>
+      </c>
+      <c r="N9" s="5">
+        <v>527953.5648822784</v>
+      </c>
+      <c r="O9" s="4">
+        <v>29.33727299857071</v>
+      </c>
+      <c r="P9" s="5">
+        <v>17996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>99.14529914529915</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.8547008547008548</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.08259112296132302</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.08170348297270846</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.08616905934455828</v>
+      </c>
+      <c r="K10" s="4">
+        <v>90.02471073899645</v>
+      </c>
+      <c r="L10" s="4">
+        <v>92.61333868716406</v>
+      </c>
+      <c r="M10" s="5">
+        <v>117</v>
+      </c>
+      <c r="N10" s="5">
+        <v>629610.209941864</v>
+      </c>
+      <c r="O10" s="4">
+        <v>83.7136298287281</v>
+      </c>
+      <c r="P10" s="5">
+        <v>7521</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>94.01709401709401</v>
+      </c>
+      <c r="C11" s="3">
+        <v>5.128205128205128</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.8547008547008548</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0.8547008547008548</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.1279986901599015</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1230986418928498</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.143195175926153</v>
+      </c>
+      <c r="K11" s="4">
+        <v>91.97017268445818</v>
+      </c>
+      <c r="L11" s="4">
+        <v>91.52698904376885</v>
+      </c>
+      <c r="M11" s="5">
+        <v>117</v>
+      </c>
+      <c r="N11" s="5">
+        <v>316071.172952652</v>
+      </c>
+      <c r="O11" s="4">
+        <v>37.4669479555064</v>
+      </c>
+      <c r="P11" s="5">
+        <v>8436</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>99.14529914529915</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.8547008547008548</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.09280163479583449</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.09117215093173035</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1137863273022566</v>
+      </c>
+      <c r="K12" s="4">
+        <v>86.5236350950637</v>
+      </c>
+      <c r="L12" s="4">
+        <v>91.3983058949504</v>
+      </c>
+      <c r="M12" s="5">
+        <v>117</v>
+      </c>
+      <c r="N12" s="5">
+        <v>147769.294500351</v>
+      </c>
+      <c r="O12" s="4">
+        <v>18.29733710999888</v>
+      </c>
+      <c r="P12" s="5">
+        <v>8076</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>97.43589743589743</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2.564102564102564</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.1149178933873941</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1061336032956877</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.1184818236920523</v>
+      </c>
+      <c r="K13" s="4">
+        <v>92.15593929879647</v>
+      </c>
+      <c r="L13" s="4">
+        <v>92.44335455744861</v>
+      </c>
+      <c r="M13" s="5">
+        <v>117</v>
+      </c>
+      <c r="N13" s="5">
+        <v>595396.641254425</v>
+      </c>
+      <c r="O13" s="4">
+        <v>73.97150469057337</v>
+      </c>
+      <c r="P13" s="5">
+        <v>8049</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>100</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.02658746453863372</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.02658746453863372</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.02622336872117517</v>
+      </c>
+      <c r="K14" s="4">
+        <v>99.79301122158265</v>
+      </c>
+      <c r="L14" s="4">
+        <v>99.59980114342507</v>
+      </c>
+      <c r="M14" s="5">
+        <v>117</v>
+      </c>
+      <c r="N14" s="5">
+        <v>649672.470331192</v>
+      </c>
+      <c r="O14" s="4">
+        <v>211.2069149321171</v>
+      </c>
+      <c r="P14" s="5">
+        <v>3076</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>99.14529914529915</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.8547008547008548</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.8547008547008548</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.1293776370517954</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.1283753056151281</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.1273200393752995</v>
+      </c>
+      <c r="K15" s="4">
+        <v>89.98546427117854</v>
+      </c>
+      <c r="L15" s="4">
+        <v>93.58936117325426</v>
+      </c>
+      <c r="M15" s="5">
+        <v>117</v>
+      </c>
+      <c r="N15" s="5">
+        <v>1709341.728687286</v>
+      </c>
+      <c r="O15" s="4">
+        <v>216.9766093789396</v>
+      </c>
+      <c r="P15" s="5">
+        <v>7878</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>99.14529914529915</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.8547008547008548</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.04289060601748002</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.04005793570571083</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.03992472001156028</v>
+      </c>
+      <c r="K16" s="4">
+        <v>99.41740798883662</v>
+      </c>
+      <c r="L16" s="4">
+        <v>99.03286869730132</v>
+      </c>
+      <c r="M16" s="5">
+        <v>117</v>
+      </c>
+      <c r="N16" s="5">
+        <v>208726.4161109924</v>
+      </c>
+      <c r="O16" s="4">
+        <v>97.12722946067586</v>
+      </c>
+      <c r="P16" s="5">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>98.29059829059828</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1.70940170940171</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.08891157675600188</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.08411453264475709</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.08110371602048604</v>
+      </c>
+      <c r="K17" s="4">
+        <v>86.02854817140532</v>
+      </c>
+      <c r="L17" s="4">
+        <v>91.55366259393004</v>
+      </c>
+      <c r="M17" s="5">
+        <v>117</v>
+      </c>
+      <c r="N17" s="5">
+        <v>736611.3793849945</v>
+      </c>
+      <c r="O17" s="4">
+        <v>103.0369813099727</v>
+      </c>
+      <c r="P17" s="5">
+        <v>7149</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3537,7 +5975,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
         <v>4</v>
@@ -3581,7 +6019,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
         <v>3</v>
@@ -4178,9 +6616,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>107</v>
+      </c>
+      <c r="C3" s="5">
+        <v>4</v>
+      </c>
+      <c r="D3" s="5">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>5</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>4</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>104</v>
+      </c>
+      <c r="C4" s="5">
+        <v>8</v>
+      </c>
+      <c r="D4" s="5">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5">
+        <v>3</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>116</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>101</v>
+      </c>
+      <c r="C6" s="5">
+        <v>13</v>
+      </c>
+      <c r="D6" s="5">
+        <v>3</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>3</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>3</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>115</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>113</v>
+      </c>
+      <c r="C8" s="5">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>1</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>88</v>
+      </c>
+      <c r="C9" s="5">
+        <v>20</v>
+      </c>
+      <c r="D9" s="5">
+        <v>9</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>9</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>1</v>
+      </c>
+      <c r="L9" s="5">
+        <v>8</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>116</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>110</v>
+      </c>
+      <c r="C11" s="5">
+        <v>6</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>1</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>116</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>114</v>
+      </c>
+      <c r="C13" s="5">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>117</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>116</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>1</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>116</v>
+      </c>
+      <c r="C16" s="5">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>115</v>
+      </c>
+      <c r="C17" s="5">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4191,9 +7384,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4227,8 +7426,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4250,10 +7457,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.3563539966685206</v>
@@ -4291,10 +7516,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2716139617539939</v>
+      </c>
+      <c r="O3" s="5">
+        <v>51</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.32269024797325</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2518029140758693</v>
+      </c>
+      <c r="R3" s="5">
+        <v>51</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2508176995867487</v>
@@ -4332,10 +7575,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2094955913577223</v>
+      </c>
+      <c r="O4" s="5">
+        <v>37</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1705544768464117</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.151531519180912</v>
+      </c>
+      <c r="R4" s="5">
+        <v>37</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.3010277048552297</v>
@@ -4373,10 +7634,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.3010277048552297</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.09798083231875125</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09798083231875125</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.3042945456208075</v>
@@ -4414,9 +7693,27 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4">
+        <v>0.3042945456208075</v>
+      </c>
+      <c r="O6" s="5">
+        <v>9</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.05186839009934515</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.05186839009934515</v>
+      </c>
+      <c r="R6" s="5">
+        <v>9</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4427,14 +7724,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4445,9 +7743,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4481,8 +7785,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4504,10 +7816,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.009101285404123</v>
@@ -4545,10 +7875,28 @@
       <c r="M3" s="5">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>1.060723602254396</v>
+      </c>
+      <c r="O3" s="5">
+        <v>53</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5603575689418224</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4687225048987503</v>
+      </c>
+      <c r="R3" s="5">
+        <v>52</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.6346778084049439</v>
@@ -4586,10 +7934,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.6748098677786027</v>
+      </c>
+      <c r="O4" s="5">
+        <v>34</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2250491147639889</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.194024040344331</v>
+      </c>
+      <c r="R4" s="5">
+        <v>34</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.08531011062500227</v>
@@ -4627,10 +7993,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.06190579094531756</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.07292895243593875</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07292895243593875</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>1.752885301083454</v>
@@ -4668,9 +8052,27 @@
       <c r="M6" s="5">
         <v>2</v>
       </c>
+      <c r="N6" s="4">
+        <v>1.769543632966322</v>
+      </c>
+      <c r="O6" s="5">
+        <v>8</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1350755020662421</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.1332193164562963</v>
+      </c>
+      <c r="R6" s="5">
+        <v>8</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4681,14 +8083,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4699,9 +8102,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4735,8 +8144,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4758,10 +8175,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.276289558889811</v>
@@ -4799,10 +8234,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2734916727658283</v>
+      </c>
+      <c r="O3" s="5">
+        <v>59</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1004292116051312</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1004292116051312</v>
+      </c>
+      <c r="R3" s="5">
+        <v>59</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.4028701492273056</v>
@@ -4840,10 +8293,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.3942008408831875</v>
+      </c>
+      <c r="O4" s="5">
+        <v>38</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1101175173226028</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1041178986884448</v>
+      </c>
+      <c r="R4" s="5">
+        <v>38</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.2008658663237355</v>
@@ -4881,10 +8352,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.2008658663237355</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.01956994221636478</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.01956994221636478</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.4223256334628047</v>
@@ -4922,9 +8411,27 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4">
+        <v>-0.4223256334628047</v>
+      </c>
+      <c r="O6" s="5">
+        <v>9</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.03028493117656379</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.03028493117656379</v>
+      </c>
+      <c r="R6" s="5">
+        <v>9</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4935,14 +8442,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4953,9 +8461,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4989,8 +8503,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5012,10 +8534,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.574941500875274</v>
@@ -5053,10 +8593,28 @@
       <c r="M3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.5859455580526721</v>
+      </c>
+      <c r="O3" s="5">
+        <v>54</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3990123090173534</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3742446935672505</v>
+      </c>
+      <c r="R3" s="5">
+        <v>54</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2408469604341916</v>
@@ -5094,10 +8652,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2616012244374957</v>
+      </c>
+      <c r="O4" s="5">
+        <v>30</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1886563926711719</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1824171387335909</v>
+      </c>
+      <c r="R4" s="5">
+        <v>30</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.1011487336718773</v>
@@ -5135,10 +8711,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.05101559319141132</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.09094561503359502</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09094561503359502</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.9069340088335625</v>
@@ -5176,9 +8770,27 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4">
+        <v>0.8996493813602261</v>
+      </c>
+      <c r="O6" s="5">
+        <v>7</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.09838392395771246</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.07673560639987116</v>
+      </c>
+      <c r="R6" s="5">
+        <v>7</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5189,14 +8801,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5207,9 +8820,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5243,8 +8862,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5266,10 +8893,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.137200314710001</v>
@@ -5307,10 +8952,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1319504203164208</v>
+      </c>
+      <c r="O3" s="5">
+        <v>59</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06166205380170021</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06166205380170021</v>
+      </c>
+      <c r="R3" s="5">
+        <v>59</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.2388322036663857</v>
@@ -5348,10 +9011,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2277192314387671</v>
+      </c>
+      <c r="O4" s="5">
+        <v>37</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.05868207158377466</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.05014040202405641</v>
+      </c>
+      <c r="R4" s="5">
+        <v>37</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.146704460760381</v>
@@ -5389,10 +9070,28 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4">
+        <v>-0.146704460760381</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.02471850321718875</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.02471850321718875</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
         <v>0.2961856135029311</v>
@@ -5430,9 +9129,27 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4">
+        <v>-0.2961856135029311</v>
+      </c>
+      <c r="O6" s="5">
+        <v>9</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.01620145004725892</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.01620145004725892</v>
+      </c>
+      <c r="R6" s="5">
+        <v>9</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5443,514 +9160,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.1417547209332446</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.144069703547994</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.1255433937441668</v>
-      </c>
-      <c r="E3" s="4">
-        <v>92.85022483569712</v>
-      </c>
-      <c r="F3" s="4">
-        <v>94.54897053805034</v>
-      </c>
-      <c r="G3" s="5">
-        <v>59</v>
-      </c>
-      <c r="H3" s="5">
-        <v>58</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.3889209264455626</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3496014463238054</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3388726650448932</v>
-      </c>
-      <c r="E4" s="4">
-        <v>91.89691261119825</v>
-      </c>
-      <c r="F4" s="4">
-        <v>90.70900017208595</v>
-      </c>
-      <c r="G4" s="5">
-        <v>39</v>
-      </c>
-      <c r="H4" s="5">
-        <v>36</v>
-      </c>
-      <c r="I4" s="5">
-        <v>3</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.2131419084798267</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2131419084798267</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.2163764568121166</v>
-      </c>
-      <c r="E5" s="4">
-        <v>94.09183673469387</v>
-      </c>
-      <c r="F5" s="4">
-        <v>96.78187919463087</v>
-      </c>
-      <c r="G5" s="5">
-        <v>10</v>
-      </c>
-      <c r="H5" s="5">
-        <v>10</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.1270831209054902</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.1270831209054902</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.09189966508533429</v>
-      </c>
-      <c r="E6" s="4">
-        <v>92.82312925170066</v>
-      </c>
-      <c r="F6" s="4">
-        <v>95.27591349739002</v>
-      </c>
-      <c r="G6" s="5">
-        <v>9</v>
-      </c>
-      <c r="H6" s="5">
-        <v>9</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.8893083541338489</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.8618580939277454</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.343582806472633</v>
-      </c>
-      <c r="E3" s="4">
-        <v>81.70183327568341</v>
-      </c>
-      <c r="F3" s="4">
-        <v>78.71269859325795</v>
-      </c>
-      <c r="G3" s="5">
-        <v>59</v>
-      </c>
-      <c r="H3" s="5">
-        <v>40</v>
-      </c>
-      <c r="I3" s="5">
-        <v>11</v>
-      </c>
-      <c r="J3" s="5">
-        <v>8</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>8</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.7372505630221448</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.7841660926483121</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.946502594950855</v>
-      </c>
-      <c r="E4" s="4">
-        <v>87.59113901971048</v>
-      </c>
-      <c r="F4" s="4">
-        <v>85.16893248436935</v>
-      </c>
-      <c r="G4" s="5">
-        <v>39</v>
-      </c>
-      <c r="H4" s="5">
-        <v>32</v>
-      </c>
-      <c r="I4" s="5">
-        <v>6</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.2071135850512718</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2071135850512718</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.2063948960864281</v>
-      </c>
-      <c r="E5" s="4">
-        <v>92.4251700680272</v>
-      </c>
-      <c r="F5" s="4">
-        <v>95.77181208053692</v>
-      </c>
-      <c r="G5" s="5">
-        <v>10</v>
-      </c>
-      <c r="H5" s="5">
-        <v>10</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>1.79906782756593</v>
-      </c>
-      <c r="C6" s="4">
-        <v>1.814132308164891</v>
-      </c>
-      <c r="D6" s="4">
-        <v>2.405987857947875</v>
-      </c>
-      <c r="E6" s="4">
-        <v>79.7052154195012</v>
-      </c>
-      <c r="F6" s="4">
-        <v>74.78995774297807</v>
-      </c>
-      <c r="G6" s="5">
-        <v>9</v>
-      </c>
-      <c r="H6" s="5">
-        <v>6</v>
-      </c>
-      <c r="I6" s="5">
-        <v>3</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/TettehCompressively2022.xlsx
+++ b/public/downloads/TettehCompressively2022.xlsx
@@ -1560,16 +1560,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.111996237290767</v>
+        <v>-0.1027041945388794</v>
       </c>
       <c r="O3" s="5">
         <v>58</v>
       </c>
       <c r="P3" s="4">
-        <v>0.106001456774009</v>
+        <v>0.1051063384107312</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1057690341913447</v>
+        <v>0.1050186903864912</v>
       </c>
       <c r="R3" s="5">
         <v>58</v>
@@ -1619,16 +1619,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3496014463238054</v>
+        <v>-0.3244056948325635</v>
       </c>
       <c r="O4" s="5">
         <v>36</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2171383940140157</v>
+        <v>0.2167678638854048</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1926371567166134</v>
+        <v>0.1901361031196814</v>
       </c>
       <c r="R4" s="5">
         <v>36</v>
@@ -1678,16 +1678,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2131419084798267</v>
+        <v>-0.2076657768834878</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.01505007154390796</v>
+        <v>0.01402231583978164</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.01505007154390796</v>
+        <v>0.01402231583978164</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -1737,16 +1737,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.07934986776646763</v>
+        <v>-0.1325576186536921</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
       </c>
       <c r="P6" s="4">
-        <v>0.0829998610352304</v>
+        <v>0.06101460679923439</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.0829998610352304</v>
+        <v>0.06101460679923439</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
@@ -1919,16 +1919,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.8618580939277454</v>
+        <v>0.7098726244385034</v>
       </c>
       <c r="O3" s="5">
         <v>40</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4557489181594251</v>
+        <v>0.4585085468720989</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4024170410905205</v>
+        <v>0.3933928405908144</v>
       </c>
       <c r="R3" s="5">
         <v>40</v>
@@ -1978,16 +1978,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.7841660926483121</v>
+        <v>0.7466317321313483</v>
       </c>
       <c r="O4" s="5">
         <v>32</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2057144029343028</v>
+        <v>0.1973895644856768</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1764248345659619</v>
+        <v>0.1721436815374746</v>
       </c>
       <c r="R4" s="5">
         <v>32</v>
@@ -2037,16 +2037,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.01090056739208478</v>
+        <v>-0.1502047453442472</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2092936985296888</v>
+        <v>0.1771644417382817</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2092936985296888</v>
+        <v>0.1771644417382817</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -2096,13 +2096,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>1.814132308164891</v>
+        <v>1.814872262194839</v>
       </c>
       <c r="O6" s="5">
         <v>6</v>
       </c>
       <c r="P6" s="4">
-        <v>0.04237221863425956</v>
+        <v>0.04245443574869828</v>
       </c>
       <c r="Q6" s="4">
         <v>0.0245014891406233</v>
@@ -2278,16 +2278,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.01967553392841112</v>
+        <v>0.0376982888128623</v>
       </c>
       <c r="O3" s="5">
         <v>59</v>
       </c>
       <c r="P3" s="4">
-        <v>0.09889051020675876</v>
+        <v>0.09605008026450039</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09889051020675876</v>
+        <v>0.09605008026450039</v>
       </c>
       <c r="R3" s="5">
         <v>59</v>
@@ -2337,16 +2337,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1808580781782845</v>
+        <v>-0.1612810822774122</v>
       </c>
       <c r="O4" s="5">
         <v>38</v>
       </c>
       <c r="P4" s="4">
-        <v>0.08273850817526113</v>
+        <v>0.08198056117276473</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08003274887354143</v>
+        <v>0.07873967179464059</v>
       </c>
       <c r="R4" s="5">
         <v>38</v>
@@ -2396,16 +2396,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.07035451038032789</v>
+        <v>-0.0832077706132992</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.03239601270482638</v>
+        <v>0.03037428772741037</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.03239601270482638</v>
+        <v>0.03037428772741037</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -2455,16 +2455,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.08117917708303996</v>
+        <v>0.07956757191351471</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
       </c>
       <c r="P6" s="4">
-        <v>0.03087325982139736</v>
+        <v>0.03058027696647672</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.03087325982139736</v>
+        <v>0.03058027696647672</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
@@ -2637,16 +2637,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.08234694753577505</v>
+        <v>-0.1038552886364528</v>
       </c>
       <c r="O3" s="5">
         <v>57</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1290145949809649</v>
+        <v>0.127932865663875</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1256727493364725</v>
+        <v>0.1245530646047479</v>
       </c>
       <c r="R3" s="5">
         <v>57</v>
@@ -2696,16 +2696,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4995726990232843</v>
+        <v>-0.4127698192950504</v>
       </c>
       <c r="O4" s="5">
         <v>35</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1506435228252336</v>
+        <v>0.1411946573833132</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1399958589206301</v>
+        <v>0.119546794030692</v>
       </c>
       <c r="R4" s="5">
         <v>35</v>
@@ -2755,16 +2755,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.366914822241094</v>
+        <v>-0.4629276667157072</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1277418796820325</v>
+        <v>0.108618146572266</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1277418796820325</v>
+        <v>0.108618146572266</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -2814,13 +2814,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.3003956737347302</v>
+        <v>-0.3041291411712592</v>
       </c>
       <c r="O6" s="5">
         <v>8</v>
       </c>
       <c r="P6" s="4">
-        <v>0.0234966064252353</v>
+        <v>0.02308177671006541</v>
       </c>
       <c r="Q6" s="4">
         <v>0.02502875462402088</v>
@@ -2996,16 +2996,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.003993283415827224</v>
+        <v>0.02622283208987142</v>
       </c>
       <c r="O3" s="5">
         <v>59</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1080936831613495</v>
+        <v>0.1069299775457664</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1080936831613495</v>
+        <v>0.1069299775457664</v>
       </c>
       <c r="R3" s="5">
         <v>59</v>
@@ -3055,16 +3055,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2054721066372878</v>
+        <v>-0.2397488206854206</v>
       </c>
       <c r="O4" s="5">
         <v>38</v>
       </c>
       <c r="P4" s="4">
-        <v>0.09723620614520948</v>
+        <v>0.09460522827922929</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.09237869149029621</v>
+        <v>0.09058049615542529</v>
       </c>
       <c r="R4" s="5">
         <v>38</v>
@@ -3114,16 +3114,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2040090338194631</v>
+        <v>-0.216061202100839</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.04593275950380985</v>
+        <v>0.04356632331433161</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.04593275950380985</v>
+        <v>0.04356632331433161</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -3173,16 +3173,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.05151922255410568</v>
+        <v>-0.06334339332153149</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
       </c>
       <c r="P6" s="4">
-        <v>0.02541381443241638</v>
+        <v>0.01930522307725684</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.02541381443241638</v>
+        <v>0.01930522307725684</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
@@ -3355,16 +3355,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.03111875376773236</v>
+        <v>0.001614123570575998</v>
       </c>
       <c r="O3" s="5">
         <v>58</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1067715328423905</v>
+        <v>0.1047718605753656</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.10330495625674</v>
+        <v>0.1007064469275541</v>
       </c>
       <c r="R3" s="5">
         <v>58</v>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3986491367604063</v>
+        <v>-0.3292981839410345</v>
       </c>
       <c r="O4" s="5">
         <v>37</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1634100531504175</v>
+        <v>0.159001789435596</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1441800620826946</v>
+        <v>0.1357848136903491</v>
       </c>
       <c r="R4" s="5">
         <v>37</v>
@@ -3473,16 +3473,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.414897991796758</v>
+        <v>-0.4038695519744948</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.023024111528905</v>
+        <v>0.02082415968359328</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.023024111528905</v>
+        <v>0.02082415968359328</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -3532,16 +3532,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.1411432300970338</v>
+        <v>-0.1734133538470246</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
       </c>
       <c r="P6" s="4">
-        <v>0.06029332227430367</v>
+        <v>0.04296074032985883</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.06029332227430367</v>
+        <v>0.04296074032985883</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
@@ -3714,16 +3714,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.03362059085391133</v>
+        <v>-0.03284584121675849</v>
       </c>
       <c r="O3" s="5">
         <v>59</v>
       </c>
       <c r="P3" s="4">
-        <v>0.02146370857655188</v>
+        <v>0.02143475483580125</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.02146370857655188</v>
+        <v>0.02143475483580125</v>
       </c>
       <c r="R3" s="5">
         <v>59</v>
@@ -3773,16 +3773,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.05027938924997699</v>
+        <v>-0.03540587145832319</v>
       </c>
       <c r="O4" s="5">
         <v>39</v>
       </c>
       <c r="P4" s="4">
-        <v>0.04365186941258798</v>
+        <v>0.04327049716151995</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04365186941258798</v>
+        <v>0.04327049716151995</v>
       </c>
       <c r="R4" s="5">
         <v>39</v>
@@ -3832,16 +3832,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.001377341231133755</v>
+        <v>0.000599848814879067</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.005145420757619945</v>
+        <v>0.004768450949345038</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.005145420757619945</v>
+        <v>0.004768450949345038</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.000919890896993378</v>
+        <v>-0.0005611563556158217</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
       </c>
       <c r="P6" s="4">
-        <v>0.01005527003738376</v>
+        <v>0.01001541064389736</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.01005527003738376</v>
+        <v>0.01001541064389736</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
@@ -4073,16 +4073,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4904073673521351</v>
+        <v>-0.3780427052012385</v>
       </c>
       <c r="O3" s="5">
         <v>59</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1999441870640629</v>
+        <v>0.1814648875998634</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1999441870640629</v>
+        <v>0.1814648875998634</v>
       </c>
       <c r="R3" s="5">
         <v>59</v>
@@ -4132,16 +4132,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.6461627511148308</v>
+        <v>-0.6605037252130188</v>
       </c>
       <c r="O4" s="5">
         <v>38</v>
       </c>
       <c r="P4" s="4">
-        <v>0.07144052944188135</v>
+        <v>0.07019293018041249</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06685612011916232</v>
+        <v>0.0659530833533966</v>
       </c>
       <c r="R4" s="5">
         <v>38</v>
@@ -4191,16 +4191,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2674173549616597</v>
+        <v>-0.2799541328469175</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.03161599085756961</v>
+        <v>0.02914571860852106</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.03161599085756961</v>
+        <v>0.02914571860852106</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -4250,16 +4250,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.8575786194833239</v>
+        <v>-0.8668928224330941</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
       </c>
       <c r="P6" s="4">
-        <v>0.02645954905236442</v>
+        <v>0.02340298177136428</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.02645954905236442</v>
+        <v>0.02340298177136428</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
@@ -4432,16 +4432,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.01489153709106969</v>
+        <v>0.01081873025378854</v>
       </c>
       <c r="O3" s="5">
         <v>59</v>
       </c>
       <c r="P3" s="4">
-        <v>0.04317676144002032</v>
+        <v>0.04289407335185567</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04317676144002032</v>
+        <v>0.04289407335185567</v>
       </c>
       <c r="R3" s="5">
         <v>59</v>
@@ -4491,16 +4491,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.03878930096734067</v>
+        <v>-0.01834497232729859</v>
       </c>
       <c r="O4" s="5">
         <v>38</v>
       </c>
       <c r="P4" s="4">
-        <v>0.05739908018576124</v>
+        <v>0.05702383720080133</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04913378329110481</v>
+        <v>0.04821065684232906</v>
       </c>
       <c r="R4" s="5">
         <v>38</v>
@@ -4550,16 +4550,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.007111130734708126</v>
+        <v>-0.006075518724330209</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.006032198138624381</v>
+        <v>0.005728990230713294</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.006032198138624381</v>
+        <v>0.005728990230713294</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -4609,16 +4609,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.05513476746295806</v>
+        <v>0.04755095357841554</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
       </c>
       <c r="P6" s="4">
-        <v>0.01909843005033679</v>
+        <v>0.01516473696452576</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.01909843005033679</v>
+        <v>0.01516473696452576</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
@@ -4791,16 +4791,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2822649109903326</v>
+        <v>-0.237983198291488</v>
       </c>
       <c r="O3" s="5">
         <v>59</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1193950713129163</v>
+        <v>0.112998208859437</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1193950713129163</v>
+        <v>0.112998208859437</v>
       </c>
       <c r="R3" s="5">
         <v>59</v>
@@ -4850,16 +4850,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3992643801400483</v>
+        <v>-0.3775697471573665</v>
       </c>
       <c r="O4" s="5">
         <v>37</v>
       </c>
       <c r="P4" s="4">
-        <v>0.0778460470660126</v>
+        <v>0.07739513721138827</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06233817862890089</v>
+        <v>0.06069021240469243</v>
       </c>
       <c r="R4" s="5">
         <v>37</v>
@@ -4909,16 +4909,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1652260498011373</v>
+        <v>-0.1666628245693289</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.006337371049706919</v>
+        <v>0.006331359760253008</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.006337371049706919</v>
+        <v>0.006331359760253008</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -4968,16 +4968,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.4597823727427645</v>
+        <v>-0.4806372717863923</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
       </c>
       <c r="P6" s="4">
-        <v>0.02877508076873371</v>
+        <v>0.02124469425766604</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.02877508076873371</v>
+        <v>0.02124469425766604</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
@@ -5114,13 +5114,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.2319399406966959</v>
+        <v>0.227651425505454</v>
       </c>
       <c r="I3" s="4">
-        <v>0.185936809921913</v>
+        <v>0.1809939418097659</v>
       </c>
       <c r="J3" s="4">
-        <v>0.1998038338228532</v>
+        <v>0.1938518978375812</v>
       </c>
       <c r="K3" s="4">
         <v>91.53235653235566</v>
@@ -5164,13 +5164,13 @@
         <v>0.8547008547008548</v>
       </c>
       <c r="H4" s="4">
-        <v>0.3742135135582791</v>
+        <v>0.3501741628619107</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3150522277158848</v>
+        <v>0.2929931741788405</v>
       </c>
       <c r="J4" s="4">
-        <v>0.3563238988960844</v>
+        <v>0.3505308893174464</v>
       </c>
       <c r="K4" s="4">
         <v>85.48898191755309</v>
@@ -5214,13 +5214,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.09135188429946133</v>
+        <v>0.09091534568780543</v>
       </c>
       <c r="I5" s="4">
-        <v>0.08922471928979626</v>
+        <v>0.08878169141499125</v>
       </c>
       <c r="J5" s="4">
-        <v>0.08757835118428076</v>
+        <v>0.08869846236716798</v>
       </c>
       <c r="K5" s="4">
         <v>89.73196116053261</v>
@@ -5264,13 +5264,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.2794379231808112</v>
+        <v>0.2561886677231877</v>
       </c>
       <c r="I6" s="4">
-        <v>0.2685973565324189</v>
+        <v>0.248412538119389</v>
       </c>
       <c r="J6" s="4">
-        <v>0.2819520998578581</v>
+        <v>0.2820703048765282</v>
       </c>
       <c r="K6" s="4">
         <v>89.78545264259523</v>
@@ -5314,13 +5314,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.05401418845012599</v>
+        <v>0.05275656317624809</v>
       </c>
       <c r="I7" s="4">
-        <v>0.05118481853728363</v>
+        <v>0.05015645586022352</v>
       </c>
       <c r="J7" s="4">
-        <v>0.04960434354934739</v>
+        <v>0.04923069383060766</v>
       </c>
       <c r="K7" s="4">
         <v>93.92406535263684</v>
@@ -5364,13 +5364,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.133504126333071</v>
+        <v>0.131150216045768</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1236021335367454</v>
+        <v>0.120578215701911</v>
       </c>
       <c r="J8" s="4">
-        <v>0.1338788825836971</v>
+        <v>0.1352785306427618</v>
       </c>
       <c r="K8" s="4">
         <v>92.63649049363318</v>
@@ -5414,13 +5414,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.3195413234089668</v>
+        <v>0.315418218970225</v>
       </c>
       <c r="I9" s="4">
-        <v>0.2725252530667299</v>
+        <v>0.2632155089211173</v>
       </c>
       <c r="J9" s="4">
-        <v>0.4484396193210226</v>
+        <v>0.4910027090975075</v>
       </c>
       <c r="K9" s="4">
         <v>84.42787371358753</v>
@@ -5464,13 +5464,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.08259112296132302</v>
+        <v>0.08071078625056188</v>
       </c>
       <c r="I10" s="4">
-        <v>0.08170348297270846</v>
+        <v>0.07963816925667465</v>
       </c>
       <c r="J10" s="4">
-        <v>0.08616905934455828</v>
+        <v>0.08210481514442537</v>
       </c>
       <c r="K10" s="4">
         <v>90.02471073899645</v>
@@ -5514,13 +5514,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.1279986901599015</v>
+        <v>0.122637163831035</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1230986418928498</v>
+        <v>0.1142733997841789</v>
       </c>
       <c r="J11" s="4">
-        <v>0.143195175926153</v>
+        <v>0.1412102431622134</v>
       </c>
       <c r="K11" s="4">
         <v>91.97017268445818</v>
@@ -5564,13 +5564,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.09280163479583449</v>
+        <v>0.09066566511904946</v>
       </c>
       <c r="I12" s="4">
-        <v>0.09117215093173035</v>
+        <v>0.08931325663745694</v>
       </c>
       <c r="J12" s="4">
-        <v>0.1137863273022566</v>
+        <v>0.1123922411437938</v>
       </c>
       <c r="K12" s="4">
         <v>86.5236350950637</v>
@@ -5614,13 +5614,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.1149178933873941</v>
+        <v>0.1109187848011921</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1061336032956877</v>
+        <v>0.1005254411240852</v>
       </c>
       <c r="J13" s="4">
-        <v>0.1184818236920523</v>
+        <v>0.1138920880326939</v>
       </c>
       <c r="K13" s="4">
         <v>92.15593929879647</v>
@@ -5664,13 +5664,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.02658746453863372</v>
+        <v>0.02641045410171007</v>
       </c>
       <c r="I14" s="4">
-        <v>0.02658746453863372</v>
+        <v>0.02641045410171007</v>
       </c>
       <c r="J14" s="4">
-        <v>0.02622336872117517</v>
+        <v>0.02601302786745611</v>
       </c>
       <c r="K14" s="4">
         <v>99.79301122158265</v>
@@ -5714,13 +5714,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.1293776370517954</v>
+        <v>0.1191968945936369</v>
       </c>
       <c r="I15" s="4">
-        <v>0.1283753056151281</v>
+        <v>0.1182304272228319</v>
       </c>
       <c r="J15" s="4">
-        <v>0.1273200393752995</v>
+        <v>0.1173752835008217</v>
       </c>
       <c r="K15" s="4">
         <v>89.98546427117854</v>
@@ -5764,13 +5764,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.04289060601748002</v>
+        <v>0.04229446592802223</v>
       </c>
       <c r="I16" s="4">
-        <v>0.04005793570571083</v>
+        <v>0.03928041226513667</v>
       </c>
       <c r="J16" s="4">
-        <v>0.03992472001156028</v>
+        <v>0.03980933678861494</v>
       </c>
       <c r="K16" s="4">
         <v>99.41740798883662</v>
@@ -5814,13 +5814,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.08891157675600188</v>
+        <v>0.08495573093908075</v>
       </c>
       <c r="I17" s="4">
-        <v>0.08411453264475709</v>
+        <v>0.07971259154436457</v>
       </c>
       <c r="J17" s="4">
-        <v>0.08110371602048604</v>
+        <v>0.07794533569041313</v>
       </c>
       <c r="K17" s="4">
         <v>86.02854817140532</v>
@@ -7517,16 +7517,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2716139617539939</v>
+        <v>0.2589846013940473</v>
       </c>
       <c r="O3" s="5">
         <v>51</v>
       </c>
       <c r="P3" s="4">
-        <v>0.32269024797325</v>
+        <v>0.3207309278121273</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2518029140758693</v>
+        <v>0.2515173257106405</v>
       </c>
       <c r="R3" s="5">
         <v>51</v>
@@ -7576,16 +7576,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2094955913577223</v>
+        <v>-0.1454128446057155</v>
       </c>
       <c r="O4" s="5">
         <v>37</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1705544768464117</v>
+        <v>0.164400886545972</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.151531519180912</v>
+        <v>0.1415813701208806</v>
       </c>
       <c r="R4" s="5">
         <v>37</v>
@@ -7635,16 +7635,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3010277048552297</v>
+        <v>-0.3721404943982023</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.09798083231875125</v>
+        <v>0.0839103523828129</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09798083231875125</v>
+        <v>0.0839103523828129</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -7694,16 +7694,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.3042945456208075</v>
+        <v>0.3097561124133392</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
       </c>
       <c r="P6" s="4">
-        <v>0.05186839009934515</v>
+        <v>0.0512615493446194</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.05186839009934515</v>
+        <v>0.0512615493446194</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
@@ -7876,16 +7876,16 @@
         <v>6</v>
       </c>
       <c r="N3" s="4">
-        <v>1.060723602254396</v>
+        <v>0.8707447408593794</v>
       </c>
       <c r="O3" s="5">
         <v>53</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5603575689418224</v>
+        <v>0.5172535093297267</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4687225048987503</v>
+        <v>0.4307762946501233</v>
       </c>
       <c r="R3" s="5">
         <v>52</v>
@@ -7935,16 +7935,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.6748098677786027</v>
+        <v>0.6939498092187506</v>
       </c>
       <c r="O4" s="5">
         <v>34</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2250491147639889</v>
+        <v>0.2256926775035052</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.194024040344331</v>
+        <v>0.1919475473925779</v>
       </c>
       <c r="R4" s="5">
         <v>34</v>
@@ -7994,16 +7994,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.06190579094531756</v>
+        <v>-0.10748449206055</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.07292895243593875</v>
+        <v>0.06460077663281538</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.07292895243593875</v>
+        <v>0.06460077663281538</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -8053,16 +8053,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>1.769543632966322</v>
+        <v>1.725318046328141</v>
       </c>
       <c r="O6" s="5">
         <v>8</v>
       </c>
       <c r="P6" s="4">
-        <v>0.1350755020662421</v>
+        <v>0.1115997572694249</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.1332193164562963</v>
+        <v>0.1123373018896494</v>
       </c>
       <c r="R6" s="5">
         <v>8</v>
@@ -8235,16 +8235,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2734916727658283</v>
+        <v>-0.2836301351129009</v>
       </c>
       <c r="O3" s="5">
         <v>59</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1004292116051312</v>
+        <v>0.1002573732602656</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1004292116051312</v>
+        <v>0.1002573732602656</v>
       </c>
       <c r="R3" s="5">
         <v>59</v>
@@ -8294,16 +8294,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3942008408831875</v>
+        <v>-0.3938846249695445</v>
       </c>
       <c r="O4" s="5">
         <v>38</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1101175173226028</v>
+        <v>0.1101237202112861</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1041178986884448</v>
+        <v>0.1041159433396292</v>
       </c>
       <c r="R4" s="5">
         <v>38</v>
@@ -8353,16 +8353,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2008658663237355</v>
+        <v>-0.2064552773258228</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.01956994221636478</v>
+        <v>0.01853871246197798</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.01956994221636478</v>
+        <v>0.01853871246197798</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -8412,16 +8412,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.4223256334628047</v>
+        <v>-0.4295722868905045</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
       </c>
       <c r="P6" s="4">
-        <v>0.03028493117656379</v>
+        <v>0.02685535669529157</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.03028493117656379</v>
+        <v>0.02685535669529157</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
@@ -8594,16 +8594,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5859455580526721</v>
+        <v>0.4128676844531256</v>
       </c>
       <c r="O3" s="5">
         <v>54</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3990123090173534</v>
+        <v>0.3612201734077017</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3742446935672505</v>
+        <v>0.3425687235640875</v>
       </c>
       <c r="R3" s="5">
         <v>54</v>
@@ -8653,16 +8653,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2616012244374957</v>
+        <v>0.2291487028320347</v>
       </c>
       <c r="O4" s="5">
         <v>30</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1886563926711719</v>
+        <v>0.1823501498126993</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1824171387335909</v>
+        <v>0.1796277766184867</v>
       </c>
       <c r="R4" s="5">
         <v>30</v>
@@ -8712,16 +8712,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.05101559319141132</v>
+        <v>-0.1043129835644621</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.09094561503359502</v>
+        <v>0.08029122451367243</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09094561503359502</v>
+        <v>0.08029122451367243</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -8771,16 +8771,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.8996493813602261</v>
+        <v>0.8716696416504135</v>
       </c>
       <c r="O6" s="5">
         <v>7</v>
       </c>
       <c r="P6" s="4">
-        <v>0.09838392395771246</v>
+        <v>0.08305731163628455</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.07673560639987116</v>
+        <v>0.05702996198660669</v>
       </c>
       <c r="R6" s="5">
         <v>7</v>
@@ -8953,16 +8953,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1319504203164208</v>
+        <v>-0.1351521716869968</v>
       </c>
       <c r="O3" s="5">
         <v>59</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06166205380170021</v>
+        <v>0.06160778682931756</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06166205380170021</v>
+        <v>0.06160778682931756</v>
       </c>
       <c r="R3" s="5">
         <v>59</v>
@@ -9012,16 +9012,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2277192314387671</v>
+        <v>-0.2421594560296683</v>
       </c>
       <c r="O4" s="5">
         <v>37</v>
       </c>
       <c r="P4" s="4">
-        <v>0.05868207158377466</v>
+        <v>0.05595305329476857</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.05014040202405641</v>
+        <v>0.04804442191353114</v>
       </c>
       <c r="R4" s="5">
         <v>37</v>
@@ -9071,16 +9071,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.146704460760381</v>
+        <v>-0.1560252581158537</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.02471850321718875</v>
+        <v>0.02286553481640681</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.02471850321718875</v>
+        <v>0.02286553481640681</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -9130,16 +9130,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.2961856135029311</v>
+        <v>-0.3005746687286148</v>
       </c>
       <c r="O6" s="5">
         <v>9</v>
       </c>
       <c r="P6" s="4">
-        <v>0.01620145004725892</v>
+        <v>0.01409267133680537</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.01620145004725892</v>
+        <v>0.01409267133680537</v>
       </c>
       <c r="R6" s="5">
         <v>9</v>
